--- a/data/processed/output_data_test.xlsx
+++ b/data/processed/output_data_test.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +417,2263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>document_number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>group_product</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>temp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mark_1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mark_2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mark_3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mark_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>71/00011421-26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ПепсиКо Холдингс</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>71/00011426-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ПепсиКо Холдингс</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B4" t="n">
+        <v>626</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Эколаб</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B5" t="n">
+        <v>625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Эколаб</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ЕК-00001357</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Торговля и Маркетинг</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Блиц-АИР</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>03-11-FZ60318</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>МАВТ-ПРО бывший Про-Вайн заводим всё в этого поставщика</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B9" t="n">
+        <v>302</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Астер-ЕК ПК</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B10" t="n">
+        <v>165</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Аква Вита</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8126821317/5362</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ЭЙЧ ЭНД ЭН ТРЕЙД бывший Данон</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HoRC-000974</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Хорека Сервис</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>05 002925 / 030</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B14" t="n">
+        <v>346</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Петухов Валерий Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>61 003086 / 30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ЕК2801/0018</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Глобал Фудс Торговый Дом</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ЕК2801/0083</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Глобал Фудс Торговый Дом</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>71/00012032-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ПепсиКо Холдингс</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>71/00012034-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ПепсиКо Холдингс</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ZPR1258650</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Агама Истра</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B21" t="n">
+        <v>164</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Граматских Ирина Николаевна</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1000054881/24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Восток-Запад</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Охлажденные</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B23" t="n">
+        <v>50396892</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Комус</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Сухие</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B24" t="n">
+        <v>50390159</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Комус</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Сухие</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MKER-003012</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Матушка ТД</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B26" t="n">
+        <v>360</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Петухов Валерий Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HoRC-001006</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Хорека Сервис</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B28" t="n">
+        <v>142019</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ИРБИТСКИЙ МОЛОЧНЫЙ ЗАВОД</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ЕК2901/0064</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Глобал Фудс Торговый Дом</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1772</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Сладкая Жизнь</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>61 003225 / 030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B33" t="n">
+        <v>173464</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Реж-Хлеб / Режевской Хлебокомбинат АО</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8126853203/5362</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ЭЙЧ ЭНД ЭН ТРЕЙД бывший Данон</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8126852426/5362</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ЭЙЧ ЭНД ЭН ТРЕЙД бывший Данон</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HoRC-001068</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Хорека Сервис</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B37" t="n">
+        <v>228936</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>СМАК</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Сухие</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Z02869</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Птицефабрика Свердловская</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>61 001734 / 029</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ожидаем документы </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Граматских Ирина Николаевна</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B41" t="n">
+        <v>29</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ермолаева Анжелика ИП</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B42" t="n">
+        <v>127</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Текскепро</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Абрис ПП</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EKB11126002675</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Симпл ЕКБ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>61 003282 / 030</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Метро кэш энд керри</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ЕК-00001449</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Торговля и Маркетинг</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B47" t="n">
+        <v>355</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Астер-ЕК ПК</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B48" t="n">
+        <v>376</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Петухов Валерий Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ЕК3001/0118</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Глобал Фудс Торговый Дом</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Крд-14183</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Кредос компания</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B51" t="n">
+        <v>379</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Петухов Валерий Владимирович ИП</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>